--- a/assets/assets/%D0%9E%D1%82%D0%B7%D1%8B%D0%B2%D1%8B%20%D0%BD%D0%B0%20%D0%BC%D0%B0%D1%84%D0%B8%D1%8E.xlsx
+++ b/assets/assets/%D0%9E%D1%82%D0%B7%D1%8B%D0%B2%D1%8B%20%D0%BD%D0%B0%20%D0%BC%D0%B0%D1%84%D0%B8%D1%8E.xlsx
@@ -1,12 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10611"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/iaroslav/sunday_sports/assets/"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{73305210-5731-F046-BAD6-32CAF54D6D14}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <bookViews>
+    <workbookView xWindow="4340" yWindow="760" windowWidth="30220" windowHeight="19900" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+  </bookViews>
   <sheets>
-    <sheet state="visible" name="Ответы на форму (1)" sheetId="1" r:id="rId4"/>
+    <sheet name="Ответы на форму (1)" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames/>
-  <calcPr/>
+  <calcPr calcId="0"/>
+  <fileRecoveryPr repairLoad="1"/>
 </workbook>
 </file>
 
@@ -298,9 +308,6 @@
     <t>Тамара Львовна</t>
   </si>
   <si>
-    <t>навострилась крутить косяки с закрытыми глазами</t>
-  </si>
-  <si>
     <t xml:space="preserve">Боль и предательство. Это все что я помню. Мафия убивала меня раз за разом, оставляя только следы моей крови за столом. Я кричала, что никого не убивала, но мои собственные друзья мне не верили. И затем я снова умирала, но теперь уже от рук своих соратников. Только глядя на их ликование и победу, уже не сидя с друзьями и врагами плечом к плечу, а стоя у них за спинами, я могла присоединиться к ликованию, ощутить горький вкус победы, доставшийся нам, но какой ценой. </t>
   </si>
   <si>
@@ -323,64 +330,77 @@
   </si>
   <si>
     <t>https://drive.google.com/open?id=1GPg_yiaP5kWNuZitjTwas2OFWiqsZD6U</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Командная игра, аналитика, мелкая моторика. </t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="x14ac x16r2 xr xr9">
   <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="m/d/yyyy h:mm:ss"/>
+    <numFmt numFmtId="164" formatCode="m/d/yyyy\ h:mm:ss"/>
   </numFmts>
-  <fonts count="10">
+  <fonts count="10" x14ac:knownFonts="1">
     <font>
-      <sz val="10.0"/>
+      <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="10"/>
       <color theme="1"/>
       <name val="Arial"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <u/>
+      <sz val="10"/>
       <color rgb="FF0000FF"/>
       <name val="Roboto"/>
     </font>
     <font>
       <u/>
+      <sz val="10"/>
       <color rgb="FF0000FF"/>
       <name val="Roboto"/>
     </font>
     <font>
       <u/>
+      <sz val="10"/>
       <color rgb="FF0000FF"/>
       <name val="Roboto"/>
     </font>
     <font>
       <u/>
+      <sz val="10"/>
       <color rgb="FF0000FF"/>
       <name val="Roboto"/>
     </font>
     <font>
       <u/>
+      <sz val="10"/>
       <color rgb="FF0000FF"/>
       <name val="Roboto"/>
     </font>
     <font>
       <u/>
+      <sz val="10"/>
       <color rgb="FF0000FF"/>
       <name val="Roboto"/>
     </font>
     <font>
       <u/>
+      <sz val="10"/>
       <color rgb="FF0000FF"/>
       <name val="Roboto"/>
     </font>
     <font>
       <u/>
+      <sz val="10"/>
       <color rgb="FF0000FF"/>
       <name val="Roboto"/>
     </font>
@@ -390,11 +410,17 @@
       <patternFill patternType="none"/>
     </fill>
     <fill>
-      <patternFill patternType="lightGray"/>
+      <patternFill patternType="gray125"/>
     </fill>
   </fills>
   <borders count="13">
-    <border/>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
     <border>
       <left style="thin">
         <color rgb="FF442F65"/>
@@ -408,6 +434,7 @@
       <bottom style="thin">
         <color rgb="FF442F65"/>
       </bottom>
+      <diagonal/>
     </border>
     <border>
       <left style="thin">
@@ -422,6 +449,7 @@
       <bottom style="thin">
         <color rgb="FF442F65"/>
       </bottom>
+      <diagonal/>
     </border>
     <border>
       <left style="thin">
@@ -436,6 +464,7 @@
       <bottom style="thin">
         <color rgb="FF442F65"/>
       </bottom>
+      <diagonal/>
     </border>
     <border>
       <left style="thin">
@@ -450,6 +479,7 @@
       <bottom style="thin">
         <color rgb="FFFFFFFF"/>
       </bottom>
+      <diagonal/>
     </border>
     <border>
       <left style="thin">
@@ -464,6 +494,7 @@
       <bottom style="thin">
         <color rgb="FFFFFFFF"/>
       </bottom>
+      <diagonal/>
     </border>
     <border>
       <left style="thin">
@@ -478,6 +509,7 @@
       <bottom style="thin">
         <color rgb="FFFFFFFF"/>
       </bottom>
+      <diagonal/>
     </border>
     <border>
       <left style="thin">
@@ -492,6 +524,7 @@
       <bottom style="thin">
         <color rgb="FFF8F9FA"/>
       </bottom>
+      <diagonal/>
     </border>
     <border>
       <left style="thin">
@@ -506,6 +539,7 @@
       <bottom style="thin">
         <color rgb="FFF8F9FA"/>
       </bottom>
+      <diagonal/>
     </border>
     <border>
       <left style="thin">
@@ -520,6 +554,7 @@
       <bottom style="thin">
         <color rgb="FFF8F9FA"/>
       </bottom>
+      <diagonal/>
     </border>
     <border>
       <left style="thin">
@@ -534,6 +569,7 @@
       <bottom style="thin">
         <color rgb="FF442F65"/>
       </bottom>
+      <diagonal/>
     </border>
     <border>
       <left style="thin">
@@ -548,6 +584,7 @@
       <bottom style="thin">
         <color rgb="FF442F65"/>
       </bottom>
+      <diagonal/>
     </border>
     <border>
       <left style="thin">
@@ -562,162 +599,134 @@
       <bottom style="thin">
         <color rgb="FF442F65"/>
       </bottom>
+      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="24">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
-    </xf>
-    <xf borderId="1" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
-    </xf>
-    <xf borderId="2" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
-    </xf>
-    <xf borderId="3" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
-    </xf>
-    <xf borderId="4" fillId="0" fontId="1" numFmtId="164" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
-    </xf>
-    <xf borderId="5" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
-    </xf>
-    <xf borderId="6" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
-    </xf>
-    <xf borderId="7" fillId="0" fontId="1" numFmtId="164" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
-    </xf>
-    <xf borderId="8" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
-    </xf>
-    <xf borderId="8" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment shrinkToFit="0" vertical="center" wrapText="0"/>
-    </xf>
-    <xf borderId="9" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
-    </xf>
-    <xf borderId="5" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
-    </xf>
-    <xf borderId="5" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment shrinkToFit="0" vertical="center" wrapText="0"/>
-    </xf>
-    <xf borderId="7" fillId="0" fontId="1" numFmtId="164" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
-    </xf>
-    <xf borderId="8" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
-    </xf>
-    <xf borderId="8" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
-    </xf>
-    <xf borderId="9" fillId="0" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
-    </xf>
-    <xf borderId="4" fillId="0" fontId="1" numFmtId="164" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
-    </xf>
-    <xf borderId="5" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
-    </xf>
-    <xf borderId="5" fillId="0" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
-    </xf>
-    <xf borderId="6" fillId="0" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
-    </xf>
-    <xf borderId="10" fillId="0" fontId="1" numFmtId="164" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
-    </xf>
-    <xf borderId="11" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
-    </xf>
-    <xf borderId="12" fillId="0" fontId="9" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
+  <cellXfs count="18">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle xfId="0" name="Normal" builtinId="0"/>
+    <cellStyle name="Обычный" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="4">
+  <dxfs count="3">
     <dxf>
-      <font/>
       <fill>
-        <patternFill patternType="none"/>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
       </fill>
-      <border/>
     </dxf>
     <dxf>
-      <font/>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
       <fill>
         <patternFill patternType="solid">
           <fgColor rgb="FF5B3F86"/>
           <bgColor rgb="FF5B3F86"/>
         </patternFill>
       </fill>
-      <border/>
-    </dxf>
-    <dxf>
-      <font/>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-      <border/>
-    </dxf>
-    <dxf>
-      <font/>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-      <border/>
     </dxf>
   </dxfs>
   <tableStyles count="1">
-    <tableStyle count="3" pivot="0" name="Ответы на форму (1)-style">
-      <tableStyleElement dxfId="1" type="headerRow"/>
-      <tableStyleElement dxfId="2" type="firstRowStripe"/>
-      <tableStyleElement dxfId="3" type="secondRowStripe"/>
+    <tableStyle name="Ответы на форму (1)-style" pivot="0" count="3" xr9:uid="{00000000-0011-0000-FFFF-FFFF00000000}">
+      <tableStyleElement type="headerRow" dxfId="2"/>
+      <tableStyleElement type="firstRowStripe" dxfId="1"/>
+      <tableStyleElement type="secondRowStripe" dxfId="0"/>
     </tableStyle>
   </tableStyles>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
-<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
-</file>
-
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A1:K16" displayName="Form_Responses1" name="Form_Responses1" id="1">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Form_Responses1" displayName="Form_Responses1" ref="A1:K16">
   <tableColumns count="11">
-    <tableColumn name="Отметка времени" id="1"/>
-    <tableColumn name="Начнем с простого. Насколько вам понарвилось?" id="2"/>
-    <tableColumn name="Кстати, кем вы работаете?" id="3"/>
-    <tableColumn name="Как вас зовут? " id="4"/>
-    <tableColumn name="Ощутили ли вы какие-то изменения после игр в своем мышлении и/или социальном поведении и/или вербальном общении?" id="5"/>
-    <tableColumn name="Как вы думаете, какие навыки вы подкачали за столом? " id="6"/>
-    <tableColumn name="Как вы оценили бы эмоциональную атмосферу, царившую за нашими столами?" id="7"/>
-    <tableColumn name="Порекомендовали ли бы вы эти игры своим друзьям?" id="8"/>
-    <tableColumn name="Наконец, самое сложное. Вы могли бы написать полноценный текстик длинной порядка 500 символов, о том как вам эти игры и как они на вас повлияли? Очень было бы круто услышать именно истории о том, как изменились ваши социальные навыки и так далее. Если приплетете сюда свою работу — будет супер круто. " id="9"/>
-    <tableColumn name="Почти закончили! Если вы хотите (если!), оставьте пожалуйста какой-то ваш контакт, чтобы продемонстрировать живость вашего отзыва. Может быть ссылка на инсту/телегу/канал/линкедин/аккаунт в Пикабу. " id="10"/>
-    <tableColumn name="При демонстрации ваших отзывов было бы неплохо использовать какие-то ваши реальные фотки. Поделитесь пожалуйста :) " id="11"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Отметка времени"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Начнем с простого. Насколько вам понарвилось?"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="Кстати, кем вы работаете?"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="Как вас зовут? "/>
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="Ощутили ли вы какие-то изменения после игр в своем мышлении и/или социальном поведении и/или вербальном общении?"/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="Как вы думаете, какие навыки вы подкачали за столом? "/>
+    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0000-000007000000}" name="Как вы оценили бы эмоциональную атмосферу, царившую за нашими столами?"/>
+    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0000-000008000000}" name="Порекомендовали ли бы вы эти игры своим друзьям?"/>
+    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0000-000009000000}" name="Наконец, самое сложное. Вы могли бы написать полноценный текстик длинной порядка 500 символов, о том как вам эти игры и как они на вас повлияли? Очень было бы круто услышать именно истории о том, как изменились ваши социальные навыки и так далее. Если при"/>
+    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0000-00000A000000}" name="Почти закончили! Если вы хотите (если!), оставьте пожалуйста какой-то ваш контакт, чтобы продемонстрировать живость вашего отзыва. Может быть ссылка на инсту/телегу/канал/линкедин/аккаунт в Пикабу. "/>
+    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0000-00000B000000}" name="При демонстрации ваших отзывов было бы неплохо использовать какие-то ваши реальные фотки. Поделитесь пожалуйста :) "/>
   </tableColumns>
-  <tableStyleInfo name="Ответы на форму (1)-style" showColumnStripes="0" showFirstColumn="1" showLastColumn="1" showRowStripes="1"/>
+  <tableStyleInfo name="Ответы на форму (1)-style" showFirstColumn="1" showLastColumn="1" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheets">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Sheets">
   <a:themeElements>
     <a:clrScheme name="Sheets">
       <a:dk1>
@@ -907,26 +916,29 @@
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
+  <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
+  <dimension ref="A1:K16"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
   <cols>
-    <col customWidth="1" min="1" max="1" width="19.0"/>
-    <col customWidth="1" min="2" max="2" width="37.63"/>
-    <col customWidth="1" min="3" max="3" width="25.75"/>
-    <col customWidth="1" min="4" max="4" width="18.88"/>
-    <col customWidth="1" min="5" max="10" width="37.63"/>
-    <col customWidth="1" min="11" max="11" width="70.75"/>
-    <col customWidth="1" min="12" max="17" width="18.88"/>
+    <col min="1" max="1" width="19" customWidth="1"/>
+    <col min="2" max="2" width="37.6640625" customWidth="1"/>
+    <col min="3" max="3" width="25.6640625" customWidth="1"/>
+    <col min="4" max="4" width="18.83203125" customWidth="1"/>
+    <col min="5" max="10" width="37.6640625" customWidth="1"/>
+    <col min="11" max="11" width="70.6640625" customWidth="1"/>
+    <col min="12" max="17" width="18.83203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -961,12 +973,12 @@
         <v>10</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A2" s="4">
-        <v>45736.68758193287</v>
+        <v>45736.687581932871</v>
       </c>
       <c r="B2" s="5">
-        <v>10.0</v>
+        <v>10</v>
       </c>
       <c r="C2" s="5" t="s">
         <v>11</v>
@@ -981,7 +993,7 @@
         <v>14</v>
       </c>
       <c r="G2" s="5">
-        <v>10.0</v>
+        <v>10</v>
       </c>
       <c r="H2" s="5" t="s">
         <v>15</v>
@@ -996,12 +1008,12 @@
         <v>18</v>
       </c>
     </row>
-    <row r="3">
+    <row r="3" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A3" s="7">
         <v>45736.69903989583</v>
       </c>
       <c r="B3" s="8">
-        <v>9.0</v>
+        <v>9</v>
       </c>
       <c r="C3" s="8" t="s">
         <v>19</v>
@@ -1016,7 +1028,7 @@
         <v>22</v>
       </c>
       <c r="G3" s="8">
-        <v>9.0</v>
+        <v>9</v>
       </c>
       <c r="H3" s="8" t="s">
         <v>15</v>
@@ -1024,17 +1036,17 @@
       <c r="I3" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="J3" s="9"/>
-      <c r="K3" s="10" t="s">
+      <c r="J3" s="8"/>
+      <c r="K3" s="9" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="4">
+    <row r="4" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A4" s="4">
-        <v>45736.70043228009</v>
+        <v>45736.700432280093</v>
       </c>
       <c r="B4" s="5">
-        <v>10.0</v>
+        <v>10</v>
       </c>
       <c r="C4" s="5" t="s">
         <v>25</v>
@@ -1049,7 +1061,7 @@
         <v>27</v>
       </c>
       <c r="G4" s="5">
-        <v>10.0</v>
+        <v>10</v>
       </c>
       <c r="H4" s="5" t="s">
         <v>15</v>
@@ -1057,19 +1069,19 @@
       <c r="I4" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="J4" s="11" t="s">
+      <c r="J4" s="10" t="s">
         <v>29</v>
       </c>
       <c r="K4" s="6" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="5">
+    <row r="5" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A5" s="7">
-        <v>45736.71187670139</v>
+        <v>45736.711876701389</v>
       </c>
       <c r="B5" s="8">
-        <v>10.0</v>
+        <v>10</v>
       </c>
       <c r="C5" s="8" t="s">
         <v>31</v>
@@ -1084,7 +1096,7 @@
         <v>33</v>
       </c>
       <c r="G5" s="8">
-        <v>10.0</v>
+        <v>10</v>
       </c>
       <c r="H5" s="8" t="s">
         <v>15</v>
@@ -1095,16 +1107,16 @@
       <c r="J5" s="8" t="s">
         <v>35</v>
       </c>
-      <c r="K5" s="10" t="s">
+      <c r="K5" s="9" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="6">
+    <row r="6" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A6" s="4">
-        <v>45736.71618703703</v>
+        <v>45736.716187037033</v>
       </c>
       <c r="B6" s="5">
-        <v>10.0</v>
+        <v>10</v>
       </c>
       <c r="C6" s="5" t="s">
         <v>37</v>
@@ -1119,7 +1131,7 @@
         <v>39</v>
       </c>
       <c r="G6" s="5">
-        <v>8.0</v>
+        <v>8</v>
       </c>
       <c r="H6" s="5" t="s">
         <v>15</v>
@@ -1127,17 +1139,17 @@
       <c r="I6" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="J6" s="12"/>
+      <c r="J6" s="5"/>
       <c r="K6" s="6" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="7">
+    <row r="7" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A7" s="7">
         <v>45736.816599513884</v>
       </c>
       <c r="B7" s="8">
-        <v>9.0</v>
+        <v>9</v>
       </c>
       <c r="C7" s="8" t="s">
         <v>42</v>
@@ -1152,7 +1164,7 @@
         <v>44</v>
       </c>
       <c r="G7" s="8">
-        <v>8.0</v>
+        <v>8</v>
       </c>
       <c r="H7" s="8" t="s">
         <v>15</v>
@@ -1163,16 +1175,16 @@
       <c r="J7" s="8" t="s">
         <v>46</v>
       </c>
-      <c r="K7" s="10" t="s">
+      <c r="K7" s="9" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="8">
+    <row r="8" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A8" s="4">
-        <v>45737.23846641203</v>
+        <v>45737.238466412033</v>
       </c>
       <c r="B8" s="5">
-        <v>9.0</v>
+        <v>9</v>
       </c>
       <c r="C8" s="5" t="s">
         <v>48</v>
@@ -1187,7 +1199,7 @@
         <v>50</v>
       </c>
       <c r="G8" s="5">
-        <v>9.0</v>
+        <v>9</v>
       </c>
       <c r="H8" s="5" t="s">
         <v>15</v>
@@ -1195,308 +1207,308 @@
       <c r="I8" s="5" t="s">
         <v>51</v>
       </c>
-      <c r="J8" s="12"/>
+      <c r="J8" s="5"/>
       <c r="K8" s="6" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" s="13">
-        <v>45737.56294505787</v>
-      </c>
-      <c r="B9" s="14">
-        <v>10.0</v>
-      </c>
-      <c r="C9" s="14" t="s">
+    <row r="9" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A9" s="7">
+        <v>45737.562945057871</v>
+      </c>
+      <c r="B9" s="8">
+        <v>10</v>
+      </c>
+      <c r="C9" s="8" t="s">
         <v>53</v>
       </c>
-      <c r="D9" s="14" t="s">
+      <c r="D9" s="8" t="s">
         <v>54</v>
       </c>
-      <c r="E9" s="14" t="s">
+      <c r="E9" s="8" t="s">
         <v>21</v>
       </c>
-      <c r="F9" s="14" t="s">
+      <c r="F9" s="8" t="s">
         <v>55</v>
       </c>
-      <c r="G9" s="14">
-        <v>10.0</v>
-      </c>
-      <c r="H9" s="14" t="s">
+      <c r="G9" s="8">
+        <v>10</v>
+      </c>
+      <c r="H9" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="I9" s="14" t="s">
+      <c r="I9" s="8" t="s">
         <v>56</v>
       </c>
-      <c r="J9" s="15" t="s">
+      <c r="J9" s="11" t="s">
         <v>57</v>
       </c>
-      <c r="K9" s="16" t="s">
+      <c r="K9" s="12" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" s="17">
-        <v>45737.57622752315</v>
-      </c>
-      <c r="B10" s="18">
-        <v>10.0</v>
-      </c>
-      <c r="C10" s="18" t="s">
+    <row r="10" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A10" s="4">
+        <v>45737.576227523146</v>
+      </c>
+      <c r="B10" s="5">
+        <v>10</v>
+      </c>
+      <c r="C10" s="5" t="s">
         <v>59</v>
       </c>
-      <c r="D10" s="18" t="s">
+      <c r="D10" s="5" t="s">
         <v>60</v>
       </c>
-      <c r="E10" s="18" t="s">
+      <c r="E10" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="F10" s="18" t="s">
+      <c r="F10" s="5" t="s">
         <v>61</v>
       </c>
-      <c r="G10" s="18">
-        <v>10.0</v>
-      </c>
-      <c r="H10" s="18" t="s">
+      <c r="G10" s="5">
+        <v>10</v>
+      </c>
+      <c r="H10" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="I10" s="18" t="s">
+      <c r="I10" s="5" t="s">
         <v>62</v>
       </c>
-      <c r="J10" s="19" t="s">
+      <c r="J10" s="13" t="s">
         <v>63</v>
       </c>
-      <c r="K10" s="20" t="s">
+      <c r="K10" s="14" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" s="13">
-        <v>45737.62182211806</v>
-      </c>
-      <c r="B11" s="14">
-        <v>10.0</v>
-      </c>
-      <c r="C11" s="14" t="s">
+    <row r="11" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A11" s="7">
+        <v>45737.621822118061</v>
+      </c>
+      <c r="B11" s="8">
+        <v>10</v>
+      </c>
+      <c r="C11" s="8" t="s">
         <v>65</v>
       </c>
-      <c r="D11" s="14" t="s">
+      <c r="D11" s="8" t="s">
         <v>66</v>
       </c>
-      <c r="E11" s="14" t="s">
+      <c r="E11" s="8" t="s">
         <v>21</v>
       </c>
-      <c r="F11" s="14" t="s">
+      <c r="F11" s="8" t="s">
         <v>67</v>
       </c>
-      <c r="G11" s="14">
-        <v>10.0</v>
-      </c>
-      <c r="H11" s="14" t="s">
+      <c r="G11" s="8">
+        <v>10</v>
+      </c>
+      <c r="H11" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="I11" s="14" t="s">
+      <c r="I11" s="8" t="s">
         <v>68</v>
       </c>
-      <c r="J11" s="15" t="s">
+      <c r="J11" s="11" t="s">
         <v>69</v>
       </c>
-      <c r="K11" s="16" t="s">
+      <c r="K11" s="12" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" s="17">
-        <v>45737.66004048611</v>
-      </c>
-      <c r="B12" s="18">
-        <v>8.0</v>
-      </c>
-      <c r="C12" s="18" t="s">
+    <row r="12" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A12" s="4">
+        <v>45737.660040486109</v>
+      </c>
+      <c r="B12" s="5">
+        <v>8</v>
+      </c>
+      <c r="C12" s="5" t="s">
         <v>71</v>
       </c>
-      <c r="D12" s="18" t="s">
+      <c r="D12" s="5" t="s">
         <v>72</v>
       </c>
-      <c r="E12" s="18" t="s">
+      <c r="E12" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="F12" s="18" t="s">
+      <c r="F12" s="5" t="s">
         <v>44</v>
       </c>
-      <c r="G12" s="18">
-        <v>7.0</v>
-      </c>
-      <c r="H12" s="18" t="s">
+      <c r="G12" s="5">
+        <v>7</v>
+      </c>
+      <c r="H12" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="I12" s="18" t="s">
+      <c r="I12" s="5" t="s">
         <v>73</v>
       </c>
-      <c r="J12" s="18" t="s">
+      <c r="J12" s="5" t="s">
         <v>74</v>
       </c>
-      <c r="K12" s="20" t="s">
+      <c r="K12" s="14" t="s">
         <v>75</v>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" s="13">
+    <row r="13" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A13" s="7">
         <v>45738.748595868055</v>
       </c>
-      <c r="B13" s="14">
-        <v>10.0</v>
-      </c>
-      <c r="C13" s="14" t="s">
+      <c r="B13" s="8">
+        <v>10</v>
+      </c>
+      <c r="C13" s="8" t="s">
         <v>76</v>
       </c>
-      <c r="D13" s="14" t="s">
+      <c r="D13" s="8" t="s">
         <v>77</v>
       </c>
-      <c r="E13" s="14" t="s">
+      <c r="E13" s="8" t="s">
         <v>21</v>
       </c>
-      <c r="F13" s="14" t="s">
+      <c r="F13" s="8" t="s">
         <v>78</v>
       </c>
-      <c r="G13" s="14">
-        <v>10.0</v>
-      </c>
-      <c r="H13" s="14" t="s">
+      <c r="G13" s="8">
+        <v>10</v>
+      </c>
+      <c r="H13" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="I13" s="14" t="s">
+      <c r="I13" s="8" t="s">
         <v>79</v>
       </c>
-      <c r="K13" s="16" t="s">
+      <c r="K13" s="12" t="s">
         <v>80</v>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" s="17">
+    <row r="14" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A14" s="4">
         <v>45738.877251365746</v>
       </c>
-      <c r="B14" s="18">
-        <v>10.0</v>
-      </c>
-      <c r="C14" s="18" t="s">
+      <c r="B14" s="5">
+        <v>10</v>
+      </c>
+      <c r="C14" s="5" t="s">
         <v>81</v>
       </c>
-      <c r="D14" s="18" t="s">
+      <c r="D14" s="5" t="s">
         <v>82</v>
       </c>
-      <c r="E14" s="18" t="s">
+      <c r="E14" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="F14" s="18" t="s">
+      <c r="F14" s="5" t="s">
         <v>61</v>
       </c>
-      <c r="G14" s="18">
-        <v>10.0</v>
-      </c>
-      <c r="H14" s="18" t="s">
+      <c r="G14" s="5">
+        <v>10</v>
+      </c>
+      <c r="H14" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="I14" s="18" t="s">
+      <c r="I14" s="5" t="s">
         <v>83</v>
       </c>
-      <c r="J14" s="18"/>
-      <c r="K14" s="20" t="s">
+      <c r="J14" s="5"/>
+      <c r="K14" s="14" t="s">
         <v>84</v>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" s="13">
-        <v>45738.8954474537</v>
-      </c>
-      <c r="B15" s="14">
-        <v>10.0</v>
-      </c>
-      <c r="C15" s="14" t="s">
+    <row r="15" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A15" s="7">
+        <v>45738.895447453702</v>
+      </c>
+      <c r="B15" s="8">
+        <v>10</v>
+      </c>
+      <c r="C15" s="8" t="s">
         <v>85</v>
       </c>
-      <c r="D15" s="14" t="s">
+      <c r="D15" s="8" t="s">
         <v>86</v>
       </c>
-      <c r="E15" s="14" t="s">
+      <c r="E15" s="8" t="s">
         <v>21</v>
       </c>
-      <c r="F15" s="14" t="s">
+      <c r="F15" s="8" t="s">
+        <v>95</v>
+      </c>
+      <c r="G15" s="8">
+        <v>10</v>
+      </c>
+      <c r="H15" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="I15" s="8" t="s">
         <v>87</v>
       </c>
-      <c r="G15" s="14">
-        <v>10.0</v>
-      </c>
-      <c r="H15" s="14" t="s">
+      <c r="K15" s="12" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="16" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A16" s="15">
+        <v>45738.968684363426</v>
+      </c>
+      <c r="B16" s="16">
+        <v>10</v>
+      </c>
+      <c r="C16" s="16" t="s">
+        <v>89</v>
+      </c>
+      <c r="D16" s="16" t="s">
+        <v>90</v>
+      </c>
+      <c r="E16" s="16" t="s">
+        <v>21</v>
+      </c>
+      <c r="F16" s="16" t="s">
+        <v>91</v>
+      </c>
+      <c r="G16" s="16">
+        <v>10</v>
+      </c>
+      <c r="H16" s="16" t="s">
         <v>15</v>
       </c>
-      <c r="I15" s="14" t="s">
-        <v>88</v>
-      </c>
-      <c r="K15" s="16" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="21">
-        <v>45738.968684363426</v>
-      </c>
-      <c r="B16" s="22">
-        <v>10.0</v>
-      </c>
-      <c r="C16" s="22" t="s">
-        <v>90</v>
-      </c>
-      <c r="D16" s="22" t="s">
-        <v>91</v>
-      </c>
-      <c r="E16" s="22" t="s">
-        <v>21</v>
-      </c>
-      <c r="F16" s="22" t="s">
+      <c r="I16" s="16" t="s">
         <v>92</v>
       </c>
-      <c r="G16" s="22">
-        <v>10.0</v>
-      </c>
-      <c r="H16" s="22" t="s">
-        <v>15</v>
-      </c>
-      <c r="I16" s="22" t="s">
+      <c r="J16" s="16" t="s">
         <v>93</v>
       </c>
-      <c r="J16" s="22" t="s">
+      <c r="K16" s="17" t="s">
         <v>94</v>
-      </c>
-      <c r="K16" s="23" t="s">
-        <v>95</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink r:id="rId1" ref="K2"/>
-    <hyperlink r:id="rId2" ref="K3"/>
-    <hyperlink r:id="rId3" ref="J4"/>
-    <hyperlink r:id="rId4" ref="K4"/>
-    <hyperlink r:id="rId5" ref="K5"/>
-    <hyperlink r:id="rId6" ref="K6"/>
-    <hyperlink r:id="rId7" ref="K7"/>
-    <hyperlink r:id="rId8" ref="K8"/>
-    <hyperlink r:id="rId9" ref="J9"/>
-    <hyperlink r:id="rId10" ref="K9"/>
-    <hyperlink r:id="rId11" ref="J10"/>
-    <hyperlink r:id="rId12" ref="K10"/>
-    <hyperlink r:id="rId13" ref="J11"/>
-    <hyperlink r:id="rId14" ref="K11"/>
-    <hyperlink r:id="rId15" ref="K12"/>
-    <hyperlink r:id="rId16" ref="K13"/>
-    <hyperlink r:id="rId17" ref="K14"/>
-    <hyperlink r:id="rId18" ref="K15"/>
-    <hyperlink r:id="rId19" ref="K16"/>
+    <hyperlink ref="K2" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
+    <hyperlink ref="K3" r:id="rId2" xr:uid="{00000000-0004-0000-0000-000001000000}"/>
+    <hyperlink ref="J4" r:id="rId3" xr:uid="{00000000-0004-0000-0000-000002000000}"/>
+    <hyperlink ref="K4" r:id="rId4" xr:uid="{00000000-0004-0000-0000-000003000000}"/>
+    <hyperlink ref="K5" r:id="rId5" xr:uid="{00000000-0004-0000-0000-000004000000}"/>
+    <hyperlink ref="K6" r:id="rId6" xr:uid="{00000000-0004-0000-0000-000005000000}"/>
+    <hyperlink ref="K7" r:id="rId7" xr:uid="{00000000-0004-0000-0000-000006000000}"/>
+    <hyperlink ref="K8" r:id="rId8" xr:uid="{00000000-0004-0000-0000-000007000000}"/>
+    <hyperlink ref="J9" r:id="rId9" xr:uid="{00000000-0004-0000-0000-000008000000}"/>
+    <hyperlink ref="K9" r:id="rId10" xr:uid="{00000000-0004-0000-0000-000009000000}"/>
+    <hyperlink ref="J10" r:id="rId11" xr:uid="{00000000-0004-0000-0000-00000A000000}"/>
+    <hyperlink ref="K10" r:id="rId12" xr:uid="{00000000-0004-0000-0000-00000B000000}"/>
+    <hyperlink ref="J11" r:id="rId13" xr:uid="{00000000-0004-0000-0000-00000C000000}"/>
+    <hyperlink ref="K11" r:id="rId14" xr:uid="{00000000-0004-0000-0000-00000D000000}"/>
+    <hyperlink ref="K12" r:id="rId15" xr:uid="{00000000-0004-0000-0000-00000E000000}"/>
+    <hyperlink ref="K13" r:id="rId16" xr:uid="{00000000-0004-0000-0000-00000F000000}"/>
+    <hyperlink ref="K14" r:id="rId17" xr:uid="{00000000-0004-0000-0000-000010000000}"/>
+    <hyperlink ref="K15" r:id="rId18" xr:uid="{00000000-0004-0000-0000-000011000000}"/>
+    <hyperlink ref="K16" r:id="rId19" xr:uid="{00000000-0004-0000-0000-000012000000}"/>
   </hyperlinks>
-  <drawing r:id="rId20"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">
-    <tablePart r:id="rId22"/>
+    <tablePart r:id="rId20"/>
   </tableParts>
 </worksheet>
 </file>